--- a/output/2026-10-04_10_Malesia_Sabah_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-04_10_Malesia_Sabah_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -474,7 +474,6 @@
           <t>Paumin Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Sabah</t>
@@ -485,8 +484,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Trading import/export di tools, machinery &amp; mechanical appliances; sede Lrg Manis, Jln Penampang, Donggongon, Penampang, Sabah. Esistenza confermata da record commerciali Panjiva. Specializzazione in aspirazione/ATEX non confermata.</t>
@@ -494,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -519,11 +516,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fornitore B2B verificato su marketplace Lapasar Mall; sede Lot 15, Lorong Mutiara Inanam, Kota Kinabalu. Vende utensili/power tools (es. Milwaukee). Possibile rivenditore attrezzature per officine metalworking.</t>
+          <t>Fornitore B2B verificato su marketplace Lapasar Mall; sede Lot 15, Lorong Mutiara Inanam, Kota Kinabalu. Vende utensili/power tools (es. Milwaukee). Possibile rivenditore attrezzature per officine metalworking. [DUPLICATO — vedi anche: 2026-10-04_Malesia_Sabah_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -538,7 +533,6 @@
           <t>Sabah Oxygen Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Sabah</t>
@@ -549,8 +543,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Gruppo Nippon Sanso Holdings / ex Leeden National Oxygen. Sede: Lot 30, Jalan 2A KKIP Timur, Industrial Zone 12 (KKIP), Kota Kinabalu. Fornitore di gas industriali, soluzioni di saldatura e prodotti di sicurezza, settore affine a metalworking.</t>
@@ -558,7 +550,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -595,7 +587,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Filiale confermata: DBKK Unit, No.7, Lot 7, Lorong Bizhub 1, Sierra Bizhub Warehouse, Batu 13.5, Jalan Tuaran, 88450 Kota Kinabalu. Distributore/produttore PPE e forniture sicurezza industriale, copre anche MRO per engineering/metalworking. Email generale aziendale, non specifica della filiale KK.</t>
+          <t>Filiale confermata: DBKK Unit, No.7, Lot 7, Lorong Bizhub 1, Sierra Bizhub Warehouse, Batu 13.5, Jalan Tuaran, 88450 Kota Kinabalu. Distributore/produttore PPE e forniture sicurezza industriale, copre anche MRO per engineering/metalworking. Email generale aziendale, non specifica della filiale KK. [DUPLICATO — vedi anche: 2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
